--- a/outputs/1. IVC DOE R2 (Final).xlsx
+++ b/outputs/1. IVC DOE R2 (Final).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,71 +489,26 @@
           <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Schema Alignment Log</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID (Reasoning)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description (Reasoning)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage (Reasoning)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category (Reasoning)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner (Reasoning)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (Reasoning)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (Reasoning)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action (Reasoning)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Data sharing from BBSRI for the smolt probability of encounter model is at risk, potentially delaying Task 2.2.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -563,7 +518,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Facilitate conversations with Umaine on data sharing; N. Johnson to continue to facilitate conversations between LGL, BBSRI, and Umaine re: data sharing.</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -578,7 +533,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -588,66 +543,21 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Ice data collection unsuccessful</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -662,7 +572,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Real time data collection implemented. If real time data collection is not successful equipment retrieved and redeployed in May 2017.</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -687,61 +597,16 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Permitting/Licensing complete for in water testing. FERC License not granted in time.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -751,7 +616,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -761,7 +626,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Initiate communication with Regulatory agencies and FERC to scope FERC License. Resource appropriately for completion by 12/17, respond to Additional Information Requests promptly after submission.</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -776,71 +641,26 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Wet Gap Generator design not yet complete</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -850,7 +670,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -860,7 +680,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Work closely with Generator vendor to develop clear specification and ensure generator design meets this specification</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -878,68 +698,23 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Timing of generator procurement from IKM could be tight for schedule</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -949,7 +724,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -959,7 +734,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Ensure Generator delivery by 2/2018 to allow adequate time for testing using project development plan with regular status reports</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -974,71 +749,26 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Buoyancy System Procurement: components are not available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1048,7 +778,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1058,7 +788,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Compile BOM and ascertain component lead times from vendors in advance of PO issue. USE COTS components.</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1076,68 +806,23 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Fabricated components have significant lead times, leading to unexpected fabrication delays.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1147,7 +832,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1157,7 +842,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Frequent vendor communication, issue PO with room for schedule creep, rapid change order resolution, contractual penalties for schedule slip.</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1172,71 +857,26 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Fabricated components have significant lead times, leading to unexpected fabrication delays.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1246,7 +886,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1256,7 +896,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Frequent vendor communication, issue PO with room for schedule creep, rapid change order resolution, contractual penalties for schedule slip.</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1274,68 +914,23 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Single source vendor for some components that require design completion and fabrication, leading to potential unexpected design/fabrication FAT delays.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1345,7 +940,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1355,7 +950,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Frequent vendor communication, issue PO with room for schedule creep, rapid change order resolution, contractual penalties for schedule slip.</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1370,71 +965,26 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>components are not available, integration of components and software is delayed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1444,7 +994,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1454,7 +1004,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Compile BOM and ascertain component lead times from vendors in advance of PO issue</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1469,71 +1019,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Fabrication delays and out of spec delivered product for power and data cable procurement.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1543,7 +1048,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1553,7 +1058,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Compile BOM and ascertain component lead times from vendors in advance of PO issue. USE COTS components where possible.</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1568,71 +1073,26 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Mooring system components are not available, leading to potential procurement delays.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1642,7 +1102,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1652,7 +1112,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Compile Bill of Materials (BOM) and ascertain component lead times from vendors in advance of Purchase Order (PO) issue. Use Commercial Off-The-Shelf (COTS) components where possible.</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1670,68 +1130,23 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Custom components require fabrication lead time, leading to potential unexpected fabrication delays.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1741,7 +1156,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1751,7 +1166,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Frequent vendor communication, issue PO with room for schedule creep, rapid change order resolution, contractual penalties for schedule slip or incorrect product delivery.</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1769,68 +1184,23 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Mechanical Brake Procurement: Custom components require fabrication lead time, risking unexpected fabrication delays.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1840,7 +1210,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1850,7 +1220,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Frequent vendor communication, issue PO with room for schedule creep, rapid change order resolution, and include contractual penalties for schedule slip or incorrect product delivery.</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1868,68 +1238,23 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Mechanical Brake Procurement: Custom components require fabrication lead time, risking unexpected fabrication delays.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1939,7 +1264,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1949,7 +1274,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Frequent vendor communication, issue PO with room for schedule creep, rapid change order resolution, and include contractual penalties for schedule slip or incorrect product delivery.</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1967,68 +1292,23 @@
         <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Buoyancy System fails some or all of validation tests</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2038,7 +1318,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2048,7 +1328,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Utilizing Incremental improvements to a proven concept, add redundancy to design. Perform land based tests in May 2017 and move on to on water validation tests prior to shipment to Igiugig. Clearly scope validation tests to ensure tests rigorously validate buoyancy system.</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2063,7 +1343,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -2071,63 +1351,18 @@
       <c r="L17" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Structural Assembly fails some or all of validation tests</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2137,7 +1372,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2147,7 +1382,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Complete thorough design and analysis, design to DNV standards, incorporate redundant structure where possible. FEA analysis of structure includes load factors following DNV standards and considers extreme loading conditions such as uneven bottom and detailed CAD models for subsystem interfaces. Validation tests to ensure structural integrity meets specs incorporate structural redundancy.</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2162,7 +1397,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -2170,63 +1405,18 @@
       <c r="L18" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Turbine Assembly fails some or all of validation tests</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2236,7 +1426,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2246,7 +1436,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Utilize CFD as design tool for performance validation, FEA analysis of turbines include load factors following DNV standards and considers extreme loading conditions, secondary design input from composite manufacturer</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2261,71 +1451,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Generator fails some or all of validation tests</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2335,7 +1480,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2345,7 +1490,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Factory Acceptance testing and laboratory testing of Generator integrated with Power electronics to ensure compatibility before assembly and commissioning</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2363,68 +1508,23 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Power Electronics fails validation, leading to unexpected failure or grid integrity issues.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2434,7 +1534,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2444,7 +1544,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Conduct factory acceptance tests and sequenced laboratory testing to ensure Power Electronics meets requirements before shipment. Implement adequate factory acceptance tests and thorough laboratory validation prior to shipment.</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2459,71 +1559,26 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>SCADA system fails validation, leading to unexpected SCADA failure or communications issues.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2533,7 +1588,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2543,7 +1598,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Conduct factory acceptance tests and sequenced laboratory testing to ensure SCADA meets requirements before shipment. Perform adequate bench tests through full length power and data cables, and laboratory validation prior to shipment.</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2558,71 +1613,26 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Power and data cables failure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2632,7 +1642,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2642,7 +1652,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Utilize proven cable technology utilize secondary cable armor in high risk areas utilize redundant conductors for data and fiber optic, reduce inspections and associated wear and tear</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2657,71 +1667,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Mooring system failure due to inadequate validation and design.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2731,7 +1696,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2741,7 +1706,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Design to DNV standards, utilize geophysical knowledge and seek industry expertise to specify mooring system components, consider most favorable failure modes.</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2756,71 +1721,26 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Driveline failure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2830,7 +1750,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2840,7 +1760,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Complete thorough validation testing and incorporate design modifications as needed. Through validation testing, design system for increased operational tolerances and loads, choose components with long service life and minimal maintenance and alignment requirements, increase modularity for replacement.</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2855,71 +1775,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Mechanical Brake Failure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2929,7 +1804,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2939,7 +1814,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Complete thorough validation testing including redundant electrical brake, and rely on third party expertise for design.</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2954,7 +1829,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
@@ -2962,63 +1837,18 @@
       <c r="L26" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Receipt of FERC Pilot license or permits are delayed and compromise deployment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3028,7 +1858,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Regulations</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3038,7 +1868,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Continue regular dialogue with regulatory agencies after final pilot license and other permit applications, respond to AIRs in timely manner</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3053,71 +1883,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Component shipment to Igiugig is delayed due to schedule slip, transportation contractor issues, weather or other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3127,7 +1912,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3137,7 +1922,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Track project schedule, align component validation and delivery to port of shipment with shipper schedules, ship components early if possible arrival on first barge of season (June 2018) or second (July 2018) at latest</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3152,71 +1937,26 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1.6-Device assembly</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Device assembly is difficult or requires modification in Igiugig due to component interfaces, component damage during shipment, or other issues.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3226,7 +1966,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Post Contract</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3236,7 +1976,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Preassemble as many components as possible prior to shipment to Igiugig. Include device assembly in validation with as many components as practical to avoid unnecessary assembly steps prior to shipment.</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3251,71 +1991,26 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Power System deployment/commissioning encounters unexpected difficulties.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3335,7 +2030,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Prior device testing and component testing in Nikiski and elsewhere will reduce unexpected issues with deployment or commissioning. These validation steps to be completed by May 2018.</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3350,71 +2045,26 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Ice accumulation on or interaction with device causes power disruption, reduction, or equipment damage</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3434,7 +2084,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Collection of in-river ice data for 2 years prior to deployment feeds engineering and IO&amp;M planning, June 2017-June 2018. On-device ice monitoring allows for operational state modification if adverse conditions or interactions occur.</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3449,71 +2099,26 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Salmon smolt data collection shows adverse reaction, or inadequate data collection does not provide regulatory agencies with adequate information to allow operation or testing during salmon smolt outmigration.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3523,7 +2128,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3533,7 +2138,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Develop rigorous fish monitoring plan in budget period 2. Consult with state and federal agencies regularly to ensure study plan and instrumentation provides adequate information for decision making. Operate device only under continuous monitoring during smolt outmigration.</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3548,71 +2153,26 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Device removal complicated by technological or environmental factors</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3632,7 +2192,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Buoyancy system includes redundant and isolated retrieval mechanisms, pre-testing in Nikiski to reduce risk of retrieval issues arising. Document results of pre-testing in Nikiski, visually inspect device during deployment with attention to buoyancy system components.</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -3647,71 +2207,26 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1. IVC DOE R2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Higher cost for maintenance and logistical support required for final design and operations plan, including training and personnel requirements, external equipment and spares.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3721,7 +2236,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3731,7 +2246,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Developing system requirements will be critical for determining technical scope for operations and maintenance technical support; involve local resources and include 3rd party input to accurately ascertain feasibility of proposed systems for logistical and technical requirements in remote environment. Develop trained leads during project who will be responsible for operating the systems after the project.</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3749,56 +2264,11 @@
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>Low</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
